--- a/docentes/Torres Sánchez José Luis - Estadisticos 20211.xlsx
+++ b/docentes/Torres Sánchez José Luis - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="25">
   <si>
     <t>Mat</t>
   </si>
@@ -70,13 +70,28 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>REYES</t>
+  </si>
+  <si>
     <t>ROMERO</t>
   </si>
   <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>VINALAY</t>
+  </si>
+  <si>
     <t>DE JESUS</t>
   </si>
   <si>
+    <t>ANGEL SAID</t>
+  </si>
+  <si>
     <t>JOSE MATEO</t>
+  </si>
+  <si>
+    <t>DIANA ARELI</t>
   </si>
 </sst>
 </file>
@@ -701,7 +716,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -733,16 +748,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920029</v>
+        <v>20330051920060</v>
       </c>
       <c r="B2" t="s">
         <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -751,21 +766,21 @@
         <v>10</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920029</v>
+        <v>20330051920060</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -774,7 +789,99 @@
         <v>10</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>20330051920029</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>20330051920029</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>20330051920033</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>20330051920033</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Torres Sánchez José Luis - Estadisticos 20211.xlsx
+++ b/docentes/Torres Sánchez José Luis - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="17">
   <si>
     <t>Mat</t>
   </si>
@@ -68,30 +68,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>VINALAY</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>ANGEL SAID</t>
-  </si>
-  <si>
-    <t>JOSE MATEO</t>
-  </si>
-  <si>
-    <t>DIANA ARELI</t>
   </si>
 </sst>
 </file>
@@ -492,10 +468,10 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F2">
         <v>18</v>
@@ -518,10 +494,10 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F3">
         <v>18</v>
@@ -583,16 +559,19 @@
         <v>36</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>36</v>
       </c>
-      <c r="E2">
-        <v>35</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
       <c r="G2">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>6.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -606,16 +585,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>69.44</v>
+      </c>
+      <c r="H3">
+        <v>6.7</v>
       </c>
     </row>
   </sheetData>
@@ -668,19 +650,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>6.7</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -694,19 +676,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>50</v>
+        <v>69.44</v>
       </c>
       <c r="H3">
-        <v>6.7</v>
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -716,7 +698,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -746,144 +728,6 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>20330051920060</v>
-      </c>
-      <c r="B2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>20330051920060</v>
-      </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>20330051920029</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>20330051920029</v>
-      </c>
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>20330051920033</v>
-      </c>
-      <c r="B6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>20330051920033</v>
-      </c>
-      <c r="B7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7">
-        <v>4</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Torres Sánchez José Luis - Estadisticos 20211.xlsx
+++ b/docentes/Torres Sánchez José Luis - Estadisticos 20211.xlsx
@@ -662,7 +662,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -679,16 +679,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G3">
-        <v>69.44</v>
+        <v>80.56</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
